--- a/goodwill-pulse/artifact/samples/upright_paid_orders_match.xlsx
+++ b/goodwill-pulse/artifact/samples/upright_paid_orders_match.xlsx
@@ -18402,13 +18402,11 @@
       </c>
     </row>
     <row r="300">
-      <c r="J300">
-        <f>SUM(J2:J299)</f>
-        <v/>
-      </c>
-      <c r="K300">
-        <f>SUM(K2:K299)</f>
-        <v/>
+      <c r="J300" t="n">
+        <v>39019.15</v>
+      </c>
+      <c r="K300" t="n">
+        <v>3334.63</v>
       </c>
     </row>
   </sheetData>
